--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_190_R19.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_190_R19.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9335</v>
+        <v>5.6316</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1384</v>
+        <v>3.8028</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7952</v>
+        <v>1.8288</v>
       </c>
       <c r="G2" t="n">
         <v>3.3783</v>
@@ -610,13 +610,13 @@
         <v>3.4793</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.5503</v>
+        <v>-0.8522</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.963</v>
+        <v>-0.2985</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5873</v>
+        <v>-0.5537</v>
       </c>
       <c r="V2" t="n">
         <v>-0.1418</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5121</v>
+        <v>3.9805</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3527</v>
+        <v>2.9556</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1593</v>
+        <v>1.0249</v>
       </c>
       <c r="G3" t="n">
         <v>2.4523</v>
@@ -688,13 +688,13 @@
         <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5236</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7512</v>
+        <v>0.3541</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2275</v>
+        <v>-0.362</v>
       </c>
       <c r="V3" t="n">
         <v>1.0722</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. NIANG</t>
+          <t>M. MORGAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7465</v>
+        <v>2.9949</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4457</v>
+        <v>2.0962</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3008</v>
+        <v>0.8988</v>
       </c>
       <c r="G4" t="n">
-        <v>4.2939</v>
+        <v>5.4713</v>
       </c>
       <c r="H4" t="n">
-        <v>2.0252</v>
+        <v>-0.4442</v>
       </c>
       <c r="I4" t="n">
-        <v>2.2687</v>
+        <v>5.9156</v>
       </c>
       <c r="J4" t="n">
-        <v>3.926</v>
+        <v>5.7006</v>
       </c>
       <c r="K4" t="n">
-        <v>2.4906</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4354</v>
+        <v>5.186</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3679</v>
+        <v>-0.2293</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4655</v>
+        <v>-0.9588</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8333</v>
+        <v>0.7296</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4639</v>
+        <v>-2.3195</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.5515</v>
+        <v>-4.639</v>
       </c>
       <c r="R4" t="n">
-        <v>3.0154</v>
+        <v>2.3195</v>
       </c>
       <c r="S4" t="n">
-        <v>0.597</v>
+        <v>-0.6929999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5351</v>
+        <v>-0.5737</v>
       </c>
       <c r="U4" t="n">
-        <v>0.062</v>
+        <v>-0.1193</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.6083</v>
+        <v>0.5361</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5361</v>
+        <v>1.6083</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.1444</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. MORGAN</t>
+          <t>S. NIANG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2879</v>
+        <v>2.9125</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6243</v>
+        <v>2.0486</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6635</v>
+        <v>0.8639</v>
       </c>
       <c r="G5" t="n">
-        <v>5.4713</v>
+        <v>4.2939</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4442</v>
+        <v>2.0252</v>
       </c>
       <c r="I5" t="n">
-        <v>5.9156</v>
+        <v>2.2687</v>
       </c>
       <c r="J5" t="n">
-        <v>5.7006</v>
+        <v>3.926</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5145999999999999</v>
+        <v>2.4906</v>
       </c>
       <c r="L5" t="n">
-        <v>5.186</v>
+        <v>1.4354</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2293</v>
+        <v>0.3679</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9588</v>
+        <v>-0.4655</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7296</v>
+        <v>0.8333</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.3195</v>
+        <v>0.4639</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.639</v>
+        <v>-2.5515</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3195</v>
+        <v>3.0154</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.4</v>
+        <v>-0.237</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0455</v>
+        <v>0.1379</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3545</v>
+        <v>-0.3749</v>
       </c>
       <c r="V5" t="n">
+        <v>-1.6083</v>
+      </c>
+      <c r="W5" t="n">
         <v>0.5361</v>
       </c>
-      <c r="W5" t="n">
-        <v>1.6083</v>
-      </c>
       <c r="X5" t="n">
-        <v>-1.0722</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.649</v>
+        <v>1.6154</v>
       </c>
       <c r="E6" t="n">
         <v>0.4475</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2015</v>
+        <v>1.1679</v>
       </c>
       <c r="G6" t="n">
         <v>1.2488</v>
@@ -922,13 +922,13 @@
         <v>2.0876</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2921</v>
+        <v>0.2585</v>
       </c>
       <c r="T6" t="n">
         <v>0.1968</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0953</v>
+        <v>0.0617</v>
       </c>
       <c r="V6" t="n">
         <v>-0.8197</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2789</v>
+        <v>-0.2617</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0191</v>
+        <v>0.0989</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2598</v>
+        <v>-0.3606</v>
       </c>
       <c r="G7" t="n">
         <v>-0.2012</v>
@@ -1000,13 +1000,13 @@
         <v>0.6959</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1498</v>
+        <v>-0.1327</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1415</v>
+        <v>-0.0235</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0083</v>
+        <v>-0.1092</v>
       </c>
       <c r="V7" t="n">
         <v>0.5361</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6937</v>
+        <v>-1.3831</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5904</v>
+        <v>-1.2798</v>
       </c>
       <c r="F8" t="n">
         <v>-0.1033</v>
@@ -1078,10 +1078,10 @@
         <v>1.8556</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4797</v>
+        <v>-0.1691</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1889</v>
+        <v>0.4995</v>
       </c>
       <c r="U8" t="n">
         <v>-0.6686</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. AKELE</t>
+          <t>L. VILDOZA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9236</v>
+        <v>-1.7245</v>
       </c>
       <c r="E9" t="n">
-        <v>1.8307</v>
+        <v>-2.2503</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.7543</v>
+        <v>0.5256999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0423</v>
+        <v>-1.1789</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9915</v>
+        <v>0.8522999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0338</v>
+        <v>-2.0312</v>
       </c>
       <c r="J9" t="n">
-        <v>1.7912</v>
+        <v>-0.6168</v>
       </c>
       <c r="K9" t="n">
-        <v>1.7176</v>
+        <v>2.7763</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0736</v>
+        <v>-3.3931</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.8335</v>
+        <v>-0.5621</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7261</v>
+        <v>-1.924</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.1074</v>
+        <v>1.3619</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1598</v>
+        <v>-2.5515</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6959</v>
+        <v>2.5515</v>
       </c>
       <c r="S9" t="n">
-        <v>0.727</v>
+        <v>-0.1513</v>
       </c>
       <c r="T9" t="n">
-        <v>1.1993</v>
+        <v>0.2401</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4722</v>
+        <v>-0.3914</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.1444</v>
+        <v>-0.3943</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.1444</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. VILDOZA</t>
+          <t>N. AKELE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1188</v>
+        <v>-2.2781</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4429</v>
+        <v>1.241</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3241</v>
+        <v>-3.5191</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1789</v>
+        <v>-0.0423</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8522999999999999</v>
+        <v>0.9915</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.0312</v>
+        <v>-1.0338</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6168</v>
+        <v>1.7912</v>
       </c>
       <c r="K10" t="n">
-        <v>2.7763</v>
+        <v>1.7176</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.3931</v>
+        <v>0.0736</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5621</v>
+        <v>-1.8335</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.924</v>
+        <v>-0.7261</v>
       </c>
       <c r="O10" t="n">
-        <v>1.3619</v>
+        <v>-1.1074</v>
       </c>
       <c r="P10" t="n">
+        <v>-0.4639</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-1.1598</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.6959</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.3725</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.6095</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-0.237</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-2.1444</v>
+      </c>
+      <c r="W10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-2.5515</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.5515</v>
-      </c>
-      <c r="S10" t="n">
-        <v>-0.5456</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0.0474</v>
-      </c>
-      <c r="U10" t="n">
-        <v>-0.593</v>
-      </c>
-      <c r="V10" t="n">
-        <v>-0.3943</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0.6778999999999999</v>
-      </c>
       <c r="X10" t="n">
-        <v>-1.0722</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="11">
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>11.114</v>
+        <v>11.4875</v>
       </c>
       <c r="E11" t="n">
-        <v>8.786899999999999</v>
+        <v>9.160500000000001</v>
       </c>
       <c r="F11" t="n">
         <v>2.327</v>
@@ -1279,7 +1279,7 @@
         <v>16.5999</v>
       </c>
       <c r="H11" t="n">
-        <v>0.05389999999999995</v>
+        <v>0.05389999999999984</v>
       </c>
       <c r="I11" t="n">
         <v>16.546</v>
@@ -1297,13 +1297,13 @@
         <v>-4.4717</v>
       </c>
       <c r="N11" t="n">
-        <v>-8.370799999999999</v>
+        <v>-8.370800000000001</v>
       </c>
       <c r="O11" t="n">
         <v>3.899100000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-2.220446049250313e-16</v>
       </c>
       <c r="Q11" t="n">
         <v>-18.5563</v>
@@ -1312,13 +1312,13 @@
         <v>18.5563</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.9857</v>
+        <v>-1.6122</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7687000000000002</v>
+        <v>1.1422</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.7541</v>
+        <v>-2.7544</v>
       </c>
       <c r="V11" t="n">
         <v>-3.5002</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.4378</v>
+        <v>5.1074</v>
       </c>
       <c r="E12" t="n">
-        <v>5.6084</v>
+        <v>5.4904</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1706</v>
+        <v>-0.383</v>
       </c>
       <c r="G12" t="n">
         <v>2.8602</v>
@@ -1390,13 +1390,13 @@
         <v>1.6237</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4178</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1142</v>
+        <v>-0.0037</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3036</v>
+        <v>0.0912</v>
       </c>
       <c r="V12" t="n">
         <v>0.5361</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. BOOKER</t>
+          <t>Z. LEDAY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.9873</v>
+        <v>1.8828</v>
       </c>
       <c r="E13" t="n">
-        <v>3.7504</v>
+        <v>2.6131</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7631</v>
+        <v>-0.7302999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1846</v>
+        <v>-1.131</v>
       </c>
       <c r="H13" t="n">
-        <v>1.2474</v>
+        <v>-0.0168</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.432</v>
+        <v>-1.1142</v>
       </c>
       <c r="J13" t="n">
-        <v>2.836</v>
+        <v>1.9004</v>
       </c>
       <c r="K13" t="n">
-        <v>2.6888</v>
+        <v>1.4354</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1472</v>
+        <v>0.465</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.0206</v>
+        <v>-3.0314</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.4414</v>
+        <v>-1.4522</v>
       </c>
       <c r="O13" t="n">
         <v>-1.5792</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.6237</v>
+        <v>2.3195</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.7112</v>
+        <v>-0.232</v>
       </c>
       <c r="R13" t="n">
-        <v>2.0876</v>
+        <v>2.5515</v>
       </c>
       <c r="S13" t="n">
-        <v>2.6512</v>
+        <v>0.805</v>
       </c>
       <c r="T13" t="n">
-        <v>2.4812</v>
+        <v>0.5192</v>
       </c>
       <c r="U13" t="n">
-        <v>0.17</v>
+        <v>0.2858</v>
       </c>
       <c r="V13" t="n">
-        <v>2.1444</v>
+        <v>-0.1107</v>
       </c>
       <c r="W13" t="n">
-        <v>2.1444</v>
+        <v>0.4254</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Z. LEDAY</t>
+          <t>D. BOOKER</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.579</v>
+        <v>1.5383</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1413</v>
+        <v>2.3349</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5623</v>
+        <v>-0.7967</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.131</v>
+        <v>-0.1846</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.0168</v>
+        <v>1.2474</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.1142</v>
+        <v>-1.432</v>
       </c>
       <c r="J14" t="n">
-        <v>1.9004</v>
+        <v>2.836</v>
       </c>
       <c r="K14" t="n">
-        <v>1.4354</v>
+        <v>2.6888</v>
       </c>
       <c r="L14" t="n">
-        <v>0.465</v>
+        <v>0.1472</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.0314</v>
+        <v>-3.0206</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.4522</v>
+        <v>-1.4414</v>
       </c>
       <c r="O14" t="n">
         <v>-1.5792</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3195</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.232</v>
+        <v>-3.7112</v>
       </c>
       <c r="R14" t="n">
-        <v>2.5515</v>
+        <v>2.0876</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5012</v>
+        <v>1.2021</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0474</v>
+        <v>1.0657</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4538</v>
+        <v>0.1364</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.1107</v>
+        <v>2.1444</v>
       </c>
       <c r="W14" t="n">
-        <v>0.4254</v>
+        <v>2.1444</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Q. ELLIS</t>
+          <t>G. RICCI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.9513</v>
+        <v>-1.5342</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0352</v>
+        <v>-1.0047</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.9162</v>
+        <v>-0.5294</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.8635</v>
+        <v>-2.1121</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2029</v>
+        <v>0.0193</v>
       </c>
       <c r="I15" t="n">
-        <v>-3.6605</v>
+        <v>-2.1314</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.725</v>
+        <v>-0.7612</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9347</v>
+        <v>0.4201</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.6597</v>
+        <v>-1.1813</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.1384</v>
+        <v>-1.3509</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1377</v>
+        <v>-0.4008</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.0008</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="P15" t="n">
         <v>1.1598</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.5515</v>
+        <v>1.1598</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2885</v>
+        <v>-0.5819</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5454</v>
+        <v>-0.2436</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.257</v>
+        <v>-0.3383</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.1507</v>
+        <v>-1.7404</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.4424</v>
+        <v>-2.0885</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2917</v>
+        <v>0.3481</v>
       </c>
       <c r="G16" t="n">
         <v>-0.676</v>
@@ -1702,13 +1702,13 @@
         <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.315</v>
+        <v>0.0953</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5228</v>
+        <v>-0.1689</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2078</v>
+        <v>0.2642</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. RICCI</t>
+          <t>Q. ELLIS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.3142</v>
+        <v>-2.6254</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3586</v>
+        <v>-0.7429</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9556</v>
+        <v>-1.8826</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.1121</v>
+        <v>-3.8635</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0193</v>
+        <v>-0.2029</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.1314</v>
+        <v>-3.6605</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.7612</v>
+        <v>-0.725</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4201</v>
+        <v>0.9347</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.1813</v>
+        <v>-1.6597</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3509</v>
+        <v>-3.1384</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4008</v>
+        <v>-1.1377</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9500999999999999</v>
+        <v>-2.0008</v>
       </c>
       <c r="P17" t="n">
         <v>1.1598</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1598</v>
+        <v>2.5515</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3618</v>
+        <v>0.6143999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5975</v>
+        <v>0.8377</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7644</v>
+        <v>-0.2234</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.0217</v>
+        <v>-2.9716</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.6239</v>
+        <v>-1.7982</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3978</v>
+        <v>-1.1733</v>
       </c>
       <c r="G18" t="n">
         <v>-3.7675</v>
@@ -1858,13 +1858,13 @@
         <v>1.8556</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5764</v>
+        <v>0.4738</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7389</v>
+        <v>0.0868</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1625</v>
+        <v>0.387</v>
       </c>
       <c r="V18" t="n">
         <v>-0.1418</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. GUDURIC</t>
+          <t>S. SHIELDS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.1096</v>
+        <v>-4.5604</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.4752</v>
+        <v>-3.184</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6344</v>
+        <v>-1.3763</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.6254</v>
+        <v>-5.1</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3602</v>
+        <v>-2.731</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.2652</v>
+        <v>-2.3691</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.0206</v>
+        <v>-1.5504</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.0736</v>
+        <v>-1.0784</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.947</v>
+        <v>-0.4721</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6048</v>
+        <v>-3.5496</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2866</v>
+        <v>-1.6526</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.3182</v>
+        <v>-1.897</v>
       </c>
       <c r="P19" t="n">
-        <v>-4.4071</v>
+        <v>0.4639</v>
       </c>
       <c r="Q19" t="n">
-        <v>-6.9585</v>
+        <v>-2.5515</v>
       </c>
       <c r="R19" t="n">
-        <v>2.5515</v>
+        <v>3.0154</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3145</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7512</v>
+        <v>0.3817</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4367</v>
+        <v>-0.306</v>
       </c>
       <c r="V19" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>3.7527</v>
+        <v>0.5361</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.1444</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. SHIELDS</t>
+          <t>M. GUDURIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.5705</v>
+        <v>-5.4242</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.8918</v>
+        <v>-3.947</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6788</v>
+        <v>-1.4772</v>
       </c>
       <c r="G20" t="n">
-        <v>-5.1</v>
+        <v>-2.6254</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.731</v>
+        <v>-0.3602</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.3691</v>
+        <v>-2.2652</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.5504</v>
+        <v>-1.0206</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.0784</v>
+        <v>-0.0736</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.4721</v>
+        <v>-0.947</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.5496</v>
+        <v>-1.6048</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.6526</v>
+        <v>-0.2866</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.897</v>
+        <v>-1.3182</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4639</v>
+        <v>-4.4071</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.5515</v>
+        <v>-6.9585</v>
       </c>
       <c r="R20" t="n">
-        <v>3.0154</v>
+        <v>2.5515</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9344</v>
+        <v>-0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.326</v>
+        <v>0.2794</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6084000000000001</v>
+        <v>-0.2794</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5361</v>
+        <v>3.7527</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5361</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="21">
@@ -2047,19 +2047,19 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-11.1139</v>
+        <v>-10.3277</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.327000000000002</v>
+        <v>-2.326900000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-8.787100000000001</v>
+        <v>-8.0007</v>
       </c>
       <c r="G21" t="n">
         <v>-16.5999</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.05399999999999938</v>
+        <v>-0.05400000000000044</v>
       </c>
       <c r="I21" t="n">
         <v>-16.5459</v>
@@ -2068,7 +2068,7 @@
         <v>4.4716</v>
       </c>
       <c r="K21" t="n">
-        <v>8.370699999999998</v>
+        <v>8.370699999999999</v>
       </c>
       <c r="L21" t="n">
         <v>-3.8991</v>
@@ -2083,7 +2083,7 @@
         <v>-12.6467</v>
       </c>
       <c r="P21" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>-18.5561</v>
@@ -2092,19 +2092,19 @@
         <v>18.5564</v>
       </c>
       <c r="S21" t="n">
-        <v>1.9856</v>
+        <v>2.7719</v>
       </c>
       <c r="T21" t="n">
-        <v>2.7542</v>
+        <v>2.7543</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7688</v>
+        <v>0.01750000000000007</v>
       </c>
       <c r="V21" t="n">
         <v>3.5002</v>
       </c>
       <c r="W21" t="n">
-        <v>9.002999999999998</v>
+        <v>9.003</v>
       </c>
       <c r="X21" t="n">
         <v>-5.502800000000001</v>
